--- a/Account-project-user-adding-Nemo.xlsx
+++ b/Account-project-user-adding-Nemo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amiralizangiabadi/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280125F3-A516-DB4F-9676-BA5FD6067434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83012A95-F87F-314F-8CA6-7E277BB2EB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="16060" xr2:uid="{0C1F4D17-60F9-4DEE-94B6-D781B29019F2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="25600" windowHeight="16060" xr2:uid="{0C1F4D17-60F9-4DEE-94B6-D781B29019F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -200,16 +200,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3352800</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3594100</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -224,14 +224,17 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11684000" y="1333500"/>
-          <a:ext cx="4711700" cy="6261100"/>
+          <a:off x="7213600" y="1600200"/>
+          <a:ext cx="4711700" cy="6604000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
@@ -277,7 +280,7 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -288,7 +291,7 @@
             </a:rPr>
             <a:t>Important Rules: </a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:schemeClr val="dk1"/>
             </a:solidFill>
@@ -299,16 +302,8 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPct val="150000"/>
-            </a:lnSpc>
-            <a:spcAft>
-              <a:spcPts val="1200"/>
-            </a:spcAft>
-          </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0">
+            <a:rPr lang="en-US" sz="1800" b="0" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -317,20 +312,12 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>1- If you are adding a new account, put the PI row before any student rows for that project. The app creates the account and project from the PI row first, then adds students to that PI’s project.</a:t>
+            <a:t>1- If you are adding a new account, put the PI row before any student rows for that project. The app creates the account and project from the PI row first, then adds other users to that PI’s project.</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPct val="150000"/>
-            </a:lnSpc>
-            <a:spcAft>
-              <a:spcPts val="1200"/>
-            </a:spcAft>
-          </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0">
+            <a:rPr lang="en-US" sz="1800" b="0" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -339,10 +326,38 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>2- Type PI in the PI column for PI rows. This tells the app to create the project using the PI’s information and indicates that a new account is being introduced into NEMO. If a PI has two emails, such</a:t>
+            <a:t>2- Type PI in the PI column for PI rows. This tells the app which row represents the PI for project creation and account linking.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3- Use the PI’s email when available. The app checks for existing users by email first. If the email is missing, it will use the UNI in column B to find the existing user and fill in missing details from NEMO.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4-</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" baseline="0">
+            <a:rPr lang="en-US" sz="1800" b="0" i="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -354,7 +369,7 @@
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0">
+            <a:rPr lang="en-US" sz="1800" b="0" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -363,10 +378,12 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>as js2334@columbia.edu</a:t>
+            <a:t>If a user does not have a UNI, you can leave that cell empty. The app will generate one automatically in the format xx{initials}{2 digits}. At least one of email or UNI should be present.</a:t>
           </a:r>
+        </a:p>
+        <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" baseline="0">
+            <a:rPr lang="en-US" sz="1800" b="0" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -375,112 +392,22 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>and</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>josh.smith@columbia.edu, always use the UNI-based address like js2334@columbia.edu.</a:t>
+            <a:t>5- Make sure the account type is entered exactly as Local, CDG, Industry, or External Academic. Do not use External Academia.</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPct val="150000"/>
-            </a:lnSpc>
-            <a:spcAft>
-              <a:spcPts val="1200"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>3- If a user does not have a UNI, you can leave that cell empty. The app will generate one automatically in this format: xx{initials}{2 digits}.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPct val="150000"/>
-            </a:lnSpc>
-            <a:spcAft>
-              <a:spcPts val="1200"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>4-</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Make sure the account type is entered correctly. Use External Academic, not External Academia, to avoid invoicing mistakes.</a:t>
-          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1800"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1800" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
